--- a/AAII_Financials/Quarterly/PANW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PANW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>PANW</t>
   </si>
@@ -656,517 +656,541 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43312</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43131</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43039</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42947</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42766</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3410000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3002000</v>
+      </c>
+      <c r="F8" s="3">
         <v>2594000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2474000</v>
       </c>
-      <c r="F8" s="3">
-        <v>2536300</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>2536000</v>
+      </c>
+      <c r="I8" s="3">
         <v>2289000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2257000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2139000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2189500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1984800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1975100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1878100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1953300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1720900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1655100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1563400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1550500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1386700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1316900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1247400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1219300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1073900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1016900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>946000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>950400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>869400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>816700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>771900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>805800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>726600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>711200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>656000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>658500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>567700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>545600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>501800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>509100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>431800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>422600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>398100</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1106000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>971000</v>
+      </c>
+      <c r="F9" s="3">
         <v>685000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>638000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>679000</v>
       </c>
-      <c r="G9" s="3">
-        <v>619300</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>619000</v>
+      </c>
+      <c r="J9" s="3">
         <v>599000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>554000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>573700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>513600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>499100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>472800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>506800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>474800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>466200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>461900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>492300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>440500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>405300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>380600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>358900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>330600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>307600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>277800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>290400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>258300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>233100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>217700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>217400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>204900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>202600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>183500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>184500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>159900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>159400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>141300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>138500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>123700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>113200</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>101200</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2304000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2031000</v>
+      </c>
+      <c r="F10" s="3">
         <v>1909000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1836000</v>
       </c>
-      <c r="F10" s="3">
-        <v>1857300</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1669700</v>
-      </c>
       <c r="H10" s="3">
+        <v>1857000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="J10" s="3">
         <v>1658000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1585000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1615800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1471200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1476000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1405300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1446500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1246100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1188900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1101500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1058200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>946200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>911600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>866800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>860400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>743300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>709300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>668200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>660000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>611100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>583600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>554200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>588400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>521700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>508600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>472500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>474000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>407800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>386200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>360500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>370600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>308100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>309400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>296900</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,127 +1232,135 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>779000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>733000</v>
+      </c>
+      <c r="F12" s="3">
         <v>511000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>528000</v>
       </c>
-      <c r="F12" s="3">
-        <v>503500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>494500</v>
-      </c>
       <c r="H12" s="3">
+        <v>504000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>494000</v>
+      </c>
+      <c r="J12" s="3">
         <v>505000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>481000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>494800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>457200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>447900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>409500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>414400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>413700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>404100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>371800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>363800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>355400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>359000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>339500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>325300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>311000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>266700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>237400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>215900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>196300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>185400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>170500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>158700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>139100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>128300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>113400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>110300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>99600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>96600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>94200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>87300</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>86000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>89900</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AQ12" s="3">
         <v>84200</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1446,43 +1478,49 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>109000</v>
+      </c>
+      <c r="F14" s="3">
         <v>5000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-12000</v>
       </c>
-      <c r="F14" s="3">
-        <v>-154100</v>
-      </c>
-      <c r="G14" s="3">
-        <v>5600</v>
-      </c>
       <c r="H14" s="3">
+        <v>-154000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J14" s="3">
         <v>11000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-37000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>27600</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L14" s="3">
-        <v>176800</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>51</v>
+      <c r="N14" s="3">
+        <v>176800</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>51</v>
@@ -1496,11 +1534,11 @@
       <c r="R14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1508,11 +1546,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>51</v>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>51</v>
@@ -1529,14 +1567,14 @@
       <c r="AC14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AD14" s="3">
-        <v>9600</v>
+      <c r="AD14" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>51</v>
+      <c r="AF14" s="3">
+        <v>9600</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>51</v>
@@ -1547,11 +1585,11 @@
       <c r="AI14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>0</v>
+      <c r="AJ14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="AL14" s="3">
         <v>0</v>
@@ -1565,53 +1603,59 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>237000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>334000</v>
+      </c>
+      <c r="F15" s="3">
         <v>91000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>89000</v>
       </c>
-      <c r="F15" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>88100</v>
-      </c>
       <c r="H15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>88000</v>
+      </c>
+      <c r="J15" s="3">
         <v>87000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>84000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>51500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>74300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>68600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>64300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>50700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>72300</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1684,8 +1728,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1724,246 +1774,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>3226000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3076000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2192000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2177000</v>
       </c>
-      <c r="F17" s="3">
-        <v>2193200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2064600</v>
-      </c>
       <c r="H17" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2064000</v>
+      </c>
+      <c r="J17" s="3">
         <v>2005000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1890000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1923500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1808100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1744700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1662900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1699800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1642200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1615200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1548200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1535100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1434300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1390800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1330100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1279700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1184300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1105700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>990500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>968200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>925900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>869600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>823700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>818300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>745300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>704600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>688100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>641400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>613000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>568100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>555300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>536400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>480900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>477000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>447100</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="F18" s="3">
         <v>402000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>297000</v>
       </c>
-      <c r="F18" s="3">
-        <v>343100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>224400</v>
-      </c>
       <c r="H18" s="3">
+        <v>343000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>225000</v>
+      </c>
+      <c r="J18" s="3">
         <v>252000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>249000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>266000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>176700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>230400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>215200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>253500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>78700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>39900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>15200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>15400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-47600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-73900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-82700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-60400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-110400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-88800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-44500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-56500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-52900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-51800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-18700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>6600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-32100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>17100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-45300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-22500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-53500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>-27300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>-49100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>-54400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>-49000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2005,246 +2069,260 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>530000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-43000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>400</v>
-      </c>
       <c r="H20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>3000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>3800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>5800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>51400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>26000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>8800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="W20" s="3">
-        <v>1000</v>
       </c>
       <c r="X20" s="3">
         <v>-500</v>
       </c>
       <c r="Y20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA20" s="3">
         <v>2400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>8100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>10800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>16200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>18800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>18200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>16000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>13000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>10200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>8600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>4900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>4800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>2900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>2100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>2700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-109000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>216000</v>
+      </c>
+      <c r="F21" s="3">
         <v>536000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>384000</v>
       </c>
-      <c r="F21" s="3">
-        <v>340900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>312100</v>
-      </c>
       <c r="H21" s="3">
+        <v>341000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>313000</v>
+      </c>
+      <c r="J21" s="3">
         <v>337000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>330000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>315300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>249500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>298400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>278600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>300400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>145200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>161200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>111900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>96700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>25700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-4300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-15300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>7900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-40700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>15900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>43500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>4800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>6300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>8400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>48500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>39800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>61400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>13400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>55700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-12100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>4500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>-27400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>-7700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>-31900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>-37300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>-32900</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2254,41 +2332,41 @@
       <c r="E22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="3">
-        <v>200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>700</v>
+      <c r="F22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="H22" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>1000</v>
       </c>
       <c r="J22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>2300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>2800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>2900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>5700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>7800</v>
-      </c>
-      <c r="P22" s="3">
-        <v>6900</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>6800</v>
       </c>
       <c r="R22" s="3">
         <v>6900</v>
@@ -2297,311 +2375,329 @@
         <v>6800</v>
       </c>
       <c r="T22" s="3">
+        <v>6900</v>
+      </c>
+      <c r="U22" s="3">
         <v>6800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="W22" s="3">
         <v>6900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>41400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>41000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>40700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>40200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>31400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>19400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>19000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>18900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>20000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>20600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>20600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>22700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>10400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>6400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>6300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>6200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>6200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>6100</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AQ22" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-269000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-156000</v>
+      </c>
+      <c r="F23" s="3">
         <v>549000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>412000</v>
       </c>
-      <c r="F23" s="3">
-        <v>591800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>310500</v>
-      </c>
       <c r="H23" s="3">
+        <v>592000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>311000</v>
+      </c>
+      <c r="J23" s="3">
         <v>325000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>368000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>319000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>251200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>135500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>282600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>316500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>131000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>84400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>34400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>17300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-52500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-80800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-91200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-102300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-150400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-130000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-82300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-48400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-67800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-61100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-54500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-13700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-21100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>2000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-41800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>16900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-43200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-24000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-55000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>-30600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>-53200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>-57800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>21000</v>
+      </c>
+      <c r="F24" s="3">
         <v>117000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>78000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>338000</v>
       </c>
-      <c r="G24" s="3">
-        <v>48400</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>49000</v>
+      </c>
+      <c r="J24" s="3">
         <v>58000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>17000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-38700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-27600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-1611400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>88400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>88800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>23200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>14400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>14000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>20700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>12700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>12400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>17000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-5300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>12300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>9900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>10500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>7000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>12600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>5100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>7100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>4600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>9900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>1600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>8200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>7600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>7700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>2800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2719,246 +2815,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-282000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="F26" s="3">
         <v>432000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>334000</v>
       </c>
-      <c r="F26" s="3">
-        <v>253800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>262100</v>
-      </c>
       <c r="H26" s="3">
+        <v>254000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>262000</v>
+      </c>
+      <c r="J26" s="3">
         <v>267000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>351000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>357700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>278800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1746900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>194200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>227700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>107800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>84200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>20000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>3300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-73200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-93500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-103600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-119300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-145100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-142300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-92200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-58900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-74800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-73700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-59600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-20800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-20200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-38300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>7000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-40400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-25600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-63200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>-38200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>-60900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>-60600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>-56900</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-282000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="F27" s="3">
         <v>432000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>334000</v>
       </c>
-      <c r="F27" s="3">
-        <v>253800</v>
-      </c>
-      <c r="G27" s="3">
-        <v>262100</v>
-      </c>
       <c r="H27" s="3">
+        <v>254000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>262000</v>
+      </c>
+      <c r="J27" s="3">
         <v>267000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>351000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>357700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>278800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1746900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>194200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>227700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>107800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>84200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>20000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>3300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-73200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-93500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-103600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-119300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-145100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-142300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-92200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-58900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-74800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-73700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-59600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-20800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-20200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-38300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>7000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-40400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-25600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-63200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>-38200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>-60900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>-60600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>-56900</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3076,8 +3190,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3195,8 +3315,14 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3314,8 +3440,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3433,246 +3565,264 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-530000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="F32" s="3">
         <v>43000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-400</v>
-      </c>
       <c r="H32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-3000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-3800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-5800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-51400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-26000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-8800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1600</v>
-      </c>
-      <c r="V32" s="3">
-        <v>500</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-1000</v>
       </c>
       <c r="X32" s="3">
         <v>500</v>
       </c>
       <c r="Y32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-16200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-18800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-18200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-10200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-8600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-4900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-4800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-282000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="F33" s="3">
         <v>432000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>334000</v>
       </c>
-      <c r="F33" s="3">
-        <v>253800</v>
-      </c>
-      <c r="G33" s="3">
-        <v>262100</v>
-      </c>
       <c r="H33" s="3">
+        <v>254000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>262000</v>
+      </c>
+      <c r="J33" s="3">
         <v>267000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>351000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>357700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>278800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1746900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>194200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>227700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>107800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>84200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>20000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>3300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-73200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-93500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-103600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-119300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-145100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-142300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-92200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-58900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-74800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-73700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-59600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-20800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-20200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-38300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>7000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-40400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-25600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-63200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>-38200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>-60900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>-60600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>-56900</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3790,251 +3940,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-282000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="F35" s="3">
         <v>432000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>334000</v>
       </c>
-      <c r="F35" s="3">
-        <v>253800</v>
-      </c>
-      <c r="G35" s="3">
-        <v>262100</v>
-      </c>
       <c r="H35" s="3">
+        <v>254000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>262000</v>
+      </c>
+      <c r="J35" s="3">
         <v>267000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>351000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>357700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>278800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1746900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>194200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>227700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>107800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>84200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>20000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>3300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-73200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-93500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-103600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-119300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-145100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-142300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-92200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-58900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-74800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-73700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-59600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-20800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-20200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-38300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>7000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-40400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-25600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-63200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>-38200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>-60900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>-60600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>-56900</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43312</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43131</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43039</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42947</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42766</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4076,8 +4244,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4119,365 +4289,385 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>2514000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2364000</v>
+      </c>
+      <c r="F41" s="3">
         <v>4158000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3066000</v>
       </c>
-      <c r="F41" s="3">
-        <v>2268600</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
+        <v>2269000</v>
+      </c>
+      <c r="I41" s="3">
         <v>2383400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2226300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2282800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1535200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1373700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1782500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2491400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1135300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1992900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1346300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2067200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2118500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2419900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1922700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2272900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1874200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1886100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2113200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2142000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2958000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1484700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2000000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1263700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>961400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1314900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>1127800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>1784400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>2506900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>949000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>915000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>842600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>744300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>692000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>761400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>839400</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>557000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>747000</v>
+      </c>
+      <c r="F42" s="3">
         <v>378000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1144000</v>
       </c>
-      <c r="F42" s="3">
-        <v>634600</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>635000</v>
+      </c>
+      <c r="I42" s="3">
         <v>916800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1006600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1108200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1043600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1516700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1588500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1402400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1254700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1965300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>2000600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1736500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>1516000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>1454700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1417600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>1188500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>1026900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1059300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>1058000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1075600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>789800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>554100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1133900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1597500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>1841700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>1733200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>1702200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>1419400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>896500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>672200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>720700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>660600</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>630700</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>680000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>593000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AQ42" s="3">
         <v>550600</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>4221000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3443000</v>
+      </c>
+      <c r="F43" s="3">
         <v>2788000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2080000</v>
       </c>
-      <c r="F43" s="3">
-        <v>3679600</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
+        <v>3680000</v>
+      </c>
+      <c r="I43" s="3">
         <v>2687300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2250400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1938000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3344500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2287700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2341800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1858900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2852000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1688800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1278100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1238100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2142500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1240600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>952200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>812100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1240400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>766800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>669200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>675500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1037100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>668800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>540300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>499200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>582400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>407500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>415000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>382300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>467000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>361800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>365100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>350800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>432100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>364100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>386100</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>346500</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
@@ -4517,11 +4707,11 @@
       <c r="O44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4595,603 +4785,639 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>562000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>518000</v>
+      </c>
+      <c r="F45" s="3">
         <v>504000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>479000</v>
       </c>
-      <c r="F45" s="3">
-        <v>477400</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
+        <v>477000</v>
+      </c>
+      <c r="I45" s="3">
         <v>424000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>386100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>372900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>373100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>341200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>338000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>334300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>358300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>339800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>780800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>691700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>637900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>582400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>576100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>565600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>505800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>428700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>435400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>407800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>344300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>306400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>304000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>289400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>279300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>261900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>242500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>229100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>536200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>222500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>209400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>185500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>169200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>159100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>139900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>129400</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>8643000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7713000</v>
+      </c>
+      <c r="F46" s="3">
         <v>8369000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7310000</v>
       </c>
-      <c r="F46" s="3">
-        <v>7522800</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
+        <v>7523000</v>
+      </c>
+      <c r="I46" s="3">
         <v>6899000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6339800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6242700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>6849700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5918800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>6446700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6477600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>6048000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>6413600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>5405800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>5733500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>6414900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>5697600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>4868600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4839100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>4647300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>4140900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4275800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>4300900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>5129200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>3014000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3978200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>3649800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>3664800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>3717500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>3487500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>3815200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>4138500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>2205500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>2210200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>2039500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>1976300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>1895200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>1880400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>1865900</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>4835000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3881000</v>
+      </c>
+      <c r="F47" s="3">
         <v>3362000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>5982000</v>
       </c>
-      <c r="F47" s="3">
-        <v>5555600</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
+        <v>5555000</v>
+      </c>
+      <c r="I47" s="3">
         <v>5152300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>4559800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>4119700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>4173200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>3504400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>3619600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2988900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>3047900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>2709800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>2820600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>2094700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1051900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>714700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>851000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>898800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>888300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>885400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>857100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>873200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>554400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>151200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>317900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>467600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>575400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>669900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>808600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>565500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>547500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>592900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>722300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>777400</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>789300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>719100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>790500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AQ47" s="3">
         <v>708400</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>1223000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1184000</v>
+      </c>
+      <c r="F48" s="3">
         <v>853000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>747000</v>
       </c>
-      <c r="F48" s="3">
-        <v>734300</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
+        <v>734000</v>
+      </c>
+      <c r="I48" s="3">
         <v>724300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>731100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>750000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>747000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>720000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>708100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>626900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>617800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>590000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>595800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>614100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>599800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>595500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>601500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>576100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>581300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>581400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>582800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>589100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>606800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>621000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>581400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>599000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>296000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>275000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>273200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>276500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>273100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>264200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>264700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>256900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>211100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>192300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>154100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>125000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>29293000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>29185000</v>
+      </c>
+      <c r="F49" s="3">
         <v>8180000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>5290000</v>
       </c>
-      <c r="F49" s="3">
-        <v>5496600</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
+        <v>5497000</v>
+      </c>
+      <c r="I49" s="3">
         <v>4781000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4822200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>4860400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3854200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3780600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3812800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3217300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3374300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3267400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3274000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3103100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>3132200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>3143400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3175200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>3203600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>3208700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>3243400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>3124600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>2357400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2171100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>2193500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>1801700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>1684500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>1632900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>1261500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>808200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>822600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>663600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>669900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>287100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>289800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>292500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>295300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>203000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>205200</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5309,8 +5535,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5428,127 +5660,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>412000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>593000</v>
+      </c>
+      <c r="F52" s="3">
         <v>427000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>390000</v>
       </c>
-      <c r="F52" s="3">
-        <v>254500</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>255000</v>
+      </c>
+      <c r="I52" s="3">
         <v>396900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>364700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>380200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>223700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1203900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>965900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>982400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>189600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>686100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1067200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>998400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1054800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>948800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>904200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>908800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>916000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>711000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>648100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>605900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>603900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>522100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>504900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>423900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>423100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>337900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>330000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>321700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>652400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>175800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>143200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>122900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>169100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>148200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>146600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5666,127 +5910,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>48460000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>46266000</v>
+      </c>
+      <c r="F54" s="3">
         <v>24979000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>23536000</v>
       </c>
-      <c r="F54" s="3">
-        <v>23576200</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
+        <v>23576000</v>
+      </c>
+      <c r="I54" s="3">
         <v>22002800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>20951700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>20374600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>19990900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>17930800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>18292000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>14808500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>14501100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>14170500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>13163400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>12543800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>12253600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>11100000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>10400500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>10426400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>10241600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>9562100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>9488400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>8726500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>9065400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>6501800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>7184100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>6824800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>6592200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>6261800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>5707500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>5801500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>5948900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>3908300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>3627500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>3486500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>3438300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>3250100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>3174600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>3006500</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5828,8 +6084,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5871,198 +6129,206 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>293000</v>
+      </c>
+      <c r="F57" s="3">
         <v>262000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>223000</v>
       </c>
-      <c r="F57" s="3">
-        <v>232200</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
+        <v>232000</v>
+      </c>
+      <c r="I57" s="3">
         <v>234800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>149300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>211600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>116300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>108900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>178800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>131800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>132300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>91600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>128300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>125900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>128000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>108000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>120400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>95300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>56900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>71800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>44700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>48500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>63600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>52300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>55400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>74700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>73300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>68600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>27900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>43000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>49400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>32700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>33400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>38800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>35500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>33200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>28000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>29200</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>219000</v>
+      </c>
+      <c r="F58" s="3">
         <v>87000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>83000</v>
       </c>
-      <c r="F58" s="3">
-        <v>79200</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>460300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>607400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>718700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>963900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1162500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1821800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1946700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1991500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3682100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3680300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3678600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>3676800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>3675700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>3673900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3672100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1557900</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="X58" s="3">
-        <v>1525600</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>51</v>
+      <c r="Z58" s="3">
+        <v>1525600</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>51</v>
@@ -6073,327 +6339,345 @@
       <c r="AC58" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE58" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
         <v>158100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>156300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>239900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>550400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>543800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>537400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>531000</v>
-      </c>
-      <c r="AL58" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AM58" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="AN58" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AO58" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP58" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AQ58" s="3">
         <v>506200</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7887000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7242000</v>
+      </c>
+      <c r="F59" s="3">
         <v>6409000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>6307000</v>
       </c>
-      <c r="F59" s="3">
-        <v>6581800</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
+        <v>6582000</v>
+      </c>
+      <c r="I59" s="3">
         <v>6110100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5940900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5758000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5556400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5040200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>4934400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>4776600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>4693300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4165500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4666500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>4390600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>4501500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>3893500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>3612100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>3377000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>3501900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2935500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2806000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2586600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>2628100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2283400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2184100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1976900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1980000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1772100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>1684000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>1532800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>1501900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>1366600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>1285600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>1173200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>1165800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>1021500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>965600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>865500</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9923000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9006000</v>
+      </c>
+      <c r="F60" s="3">
         <v>8009000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7418000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7988000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7705600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7552200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7402700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7682700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7084800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>7765500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>7513400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7737500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>8641200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>8475100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>8195100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>8306300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>7677200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>7406400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>7144400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>5116700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3007300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>4376300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2635100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2691700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2335700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2239500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2051600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2053300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>1998800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1868200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>1815700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>2101700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>1943100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>1856400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>1743000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>1201300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>1054700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>993600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>1400900</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1911000</v>
+      </c>
+      <c r="F61" s="3">
         <v>372000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>346000</v>
       </c>
-      <c r="F61" s="3">
-        <v>338200</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>338000</v>
+      </c>
+      <c r="I61" s="3">
         <v>345700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>363000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>379600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>380500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>369800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>362700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>275800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>279200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>264500</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -6407,186 +6691,198 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>1668100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>3190600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1629100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>3119200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>3084100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1477000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1461200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1445500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1430000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1414700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>1399500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>1384500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>1369700</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
       <c r="AL61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
         <v>524700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>518400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>512300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1285000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>930000</v>
+      </c>
+      <c r="F62" s="3">
         <v>949000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>913000</v>
       </c>
-      <c r="F62" s="3">
-        <v>886800</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
+        <v>887000</v>
+      </c>
+      <c r="I62" s="3">
         <v>878000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>882600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>843800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>430900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>352700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>317800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>138000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>86100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>89500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3959300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3840700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3737300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3085200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2876300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2763100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2822300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2367000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2445700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2225200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2187800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1944400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1874900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1811300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1522600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1394800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1368000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1348300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>1317200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>1243100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>1138000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>1078000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>952700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>863900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>798100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>748700</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6704,8 +7000,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6823,8 +7125,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6942,127 +7250,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20968000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>18598000</v>
+      </c>
+      <c r="F66" s="3">
         <v>15586000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>14871000</v>
       </c>
-      <c r="F66" s="3">
-        <v>15751800</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
+        <v>15752000</v>
+      </c>
+      <c r="I66" s="3">
         <v>14772300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>14576400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>14462800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>14821200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>13463000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>13934800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>12638000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>12752700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>12938100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>12434400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>12035800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>12043600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>10762400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>10282700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>9907500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>9607100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>8564900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>8451100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>7979500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>7963600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>5757100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>5575600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>5308400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>5005900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>4808300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>4635700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>4548500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>4788600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>3186200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>2994400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>2821000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>2678700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>2437000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>2304000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>2149600</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7104,8 +7424,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7223,8 +7545,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7342,8 +7670,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7461,8 +7795,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7580,127 +7920,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2791000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3073000</v>
+      </c>
+      <c r="F72" s="3">
         <v>3250000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2818000</v>
       </c>
-      <c r="F72" s="3">
-        <v>2484100</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
+        <v>2484000</v>
+      </c>
+      <c r="I72" s="3">
         <v>2230300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1968200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1700900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1350200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>992500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>713700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1033200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1227400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-1455100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1562900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-1647100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-1667100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-1670400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-1597200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-1503700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-1666800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-1547500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-1402400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-1260100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-1167900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-1109000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-1034200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-960500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-900900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-880100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-859900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-857300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-790700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-982300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-935600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>-900700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>-836700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>-798500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>-737600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>-683400</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7818,8 +8170,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7937,8 +8295,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8056,127 +8420,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27492000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>27668000</v>
+      </c>
+      <c r="F76" s="3">
         <v>9393000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8665000</v>
       </c>
-      <c r="F76" s="3">
-        <v>7824400</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>7824000</v>
+      </c>
+      <c r="I76" s="3">
         <v>7230500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6375300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5911800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5169700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4467800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4357200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2170500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1748400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1232400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>729000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>508000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>210000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>337600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>117800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>518900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>634500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>997200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1037300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>747000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1101800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>744700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1608500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1516400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1586300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1453500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1071800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>1253000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>1160300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>722100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>633100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>665500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>759600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>813100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>870600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8294,251 +8670,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43312</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43131</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43039</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42947</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42766</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-282000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="F81" s="3">
         <v>432000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>334000</v>
       </c>
-      <c r="F81" s="3">
-        <v>253800</v>
-      </c>
-      <c r="G81" s="3">
-        <v>262100</v>
-      </c>
       <c r="H81" s="3">
+        <v>254000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>262000</v>
+      </c>
+      <c r="J81" s="3">
         <v>267000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>351000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>357700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>278800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1746900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>194200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>227700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>107800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>84200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>20000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>3300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-73200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-93500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-103600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-119300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-145100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-142300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-92200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-58900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-74800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-73700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-59600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-20800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-20200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-38300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>7000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-40400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-25600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-63200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>-38200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>-60900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>-60600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>-56900</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8580,127 +8974,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>45000</v>
+      </c>
+      <c r="F83" s="3">
         <v>42000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>43000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>-1100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>40900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>40200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>39400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>-10200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>46500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>45100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>41600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>-27400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>77100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>69900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>70700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>72500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>71400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>69700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>69000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>68800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>68700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>64900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>58000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>60500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>53200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>48400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>44000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>42200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>40300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>38800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>32500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>28400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>24600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>22100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>21300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>16700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>15100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>14400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8818,8 +9220,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8937,8 +9345,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9056,8 +9470,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9175,8 +9595,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9294,127 +9720,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1357000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>871000</v>
+      </c>
+      <c r="F89" s="3">
         <v>554000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1771000</v>
       </c>
-      <c r="F89" s="3">
-        <v>1020800</v>
-      </c>
-      <c r="G89" s="3">
-        <v>628700</v>
-      </c>
       <c r="H89" s="3">
+        <v>1021000</v>
+      </c>
+      <c r="I89" s="3">
+        <v>628000</v>
+      </c>
+      <c r="J89" s="3">
         <v>557000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1510000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>512700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>528900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>690000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1526000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>414100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>432100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>694600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1236700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>523700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>389500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>482600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>588900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>325800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>277800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>364500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>534900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>333700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>169900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>306900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>225200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>231500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>296400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>275400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>252300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>277600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>241900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>244500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>274100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>239500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>211200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>214300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>203500</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9456,127 +9894,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-170000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-84000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
+        <v>-87000</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-47400</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-37400</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-36800</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-37200</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="S91" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="T91" s="3">
+        <v>-39200</v>
+      </c>
+      <c r="U91" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="V91" s="3">
+        <v>-80700</v>
+      </c>
+      <c r="W91" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="X91" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-86300</v>
       </c>
-      <c r="G91" s="3">
-        <v>-68300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-48000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-47400</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-37400</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-35200</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-36800</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-37200</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-31200</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-38300</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-39600</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-39200</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-38300</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-80700</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-34600</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-27400</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-26900</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-32100</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-29600</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-31800</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-86300</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-49100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-47200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-53100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-23500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-34300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-25400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-28800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-25600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-32200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-49200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-48600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-23800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-41800</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9694,8 +10140,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9813,127 +10265,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1006000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1766000</v>
+      </c>
+      <c r="F94" s="3">
         <v>651000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-983000</v>
       </c>
-      <c r="F94" s="3">
-        <v>-762500</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-517600</v>
-      </c>
       <c r="H94" s="3">
+        <v>-763000</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-517000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-381000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-544000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-168500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>113100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1325500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-129000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>362600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>87900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1164500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1319800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-472100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>42900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-274300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-229900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-2400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-207600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-384400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-886200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-667600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>274700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>436400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>244500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-448700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-140300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-523800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-713100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-206400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-225100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-36100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-52400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-61500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-166800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-173100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-71200</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9975,8 +10439,10 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10016,11 +10482,11 @@
       <c r="O96" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10094,8 +10560,14 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10213,8 +10685,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10332,8 +10810,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10451,127 +10935,139 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-899000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-114000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>8000</v>
       </c>
-      <c r="F100" s="3">
-        <v>-374100</v>
-      </c>
-      <c r="G100" s="3">
-        <v>47100</v>
-      </c>
       <c r="H100" s="3">
+        <v>-374000</v>
+      </c>
+      <c r="I100" s="3">
+        <v>47000</v>
+      </c>
+      <c r="J100" s="3">
         <v>-232000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-220000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-179300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1049400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-72600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-41800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1634800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>128200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-250800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>31100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-353100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>66300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-558500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>38700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-335600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-298500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-464500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>1805500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-959300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-167100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-136100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>31800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-407800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-261800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>1486400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-135200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-123400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-125700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-113800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-119400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-27100</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10611,11 +11107,11 @@
       <c r="O101" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10689,123 +11185,135 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1792000</v>
+      </c>
+      <c r="F102" s="3">
         <v>1091000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>796000</v>
       </c>
-      <c r="F102" s="3">
-        <v>-115800</v>
-      </c>
-      <c r="G102" s="3">
-        <v>158200</v>
-      </c>
       <c r="H102" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="I102" s="3">
+        <v>158000</v>
+      </c>
+      <c r="J102" s="3">
         <v>-56000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>746000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>164900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-407400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-708100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1355200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-858100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>648200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-720700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-52000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-301500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>498700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-350200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>397700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-12200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-228300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-25300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-815800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>1471600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-514700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>737200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>302600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-353300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>187900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-656200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-722600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>1557600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>34600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>73200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>98300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>52300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-69400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>-78000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>105000</v>
       </c>
     </row>
